--- a/quote_forms/039_group_insurance_quote_form--quote_forms.xlsx
+++ b/quote_forms/039_group_insurance_quote_form--quote_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1197,7 +1197,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1214,7 +1214,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1299,7 +1299,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>option 1</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1367,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>option 2</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>option 3</t>
         </is>
       </c>
     </row>
